--- a/reports/빅딜/history/2026-06-18/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/history/2026-06-18/빅딜_training_mgf_report.xlsx
@@ -20,18 +20,18 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Rangker!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Record!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">눈탱이!$A$1:$J$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">눈탱이!$A$1:$J$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">비련!$A$1:$J$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">빅딜!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">빅딜!$A$1:$J$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">치링!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">핑덤!$A$1:$J$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">핑덤!$A$1:$J$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2044" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2014" uniqueCount="684">
   <si>
     <t>guild_name</t>
   </si>
@@ -84,7 +84,7 @@
     <t>Scania 27</t>
   </si>
   <si>
-    <t>351</t>
+    <t>354</t>
   </si>
   <si>
     <t>27위</t>
@@ -117,7 +117,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>347</t>
+    <t>350</t>
   </si>
   <si>
     <t>10위</t>
@@ -147,13 +147,13 @@
     <t>Scania 3</t>
   </si>
   <si>
-    <t>345</t>
+    <t>346</t>
   </si>
   <si>
     <t>8위</t>
   </si>
   <si>
-    <t>2683조 7156억 6583만</t>
+    <t>2684조 7200억 4505만</t>
   </si>
   <si>
     <t>투력 -30조 이상- 가입 문의 Tyrael &amp;lt; 귓주셔요 자리없어도 편하게 문의주세요</t>
@@ -171,7 +171,7 @@
     <t>Scania 23</t>
   </si>
   <si>
-    <t>368</t>
+    <t>374</t>
   </si>
   <si>
     <t>7위</t>
@@ -195,7 +195,7 @@
     <t>Scania 14</t>
   </si>
   <si>
-    <t>365</t>
+    <t>371</t>
   </si>
   <si>
     <t>2435조 6389억 9855만</t>
@@ -213,7 +213,7 @@
     <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%88%88%ED%83%B1%EC%9D%B4</t>
   </si>
   <si>
-    <t>370</t>
+    <t>376</t>
   </si>
   <si>
     <t>30위</t>
@@ -237,7 +237,7 @@
     <t>Scania 43</t>
   </si>
   <si>
-    <t>697</t>
+    <t>704</t>
   </si>
   <si>
     <t>2위</t>
@@ -246,10 +246,10 @@
     <t>Lv.7</t>
   </si>
   <si>
-    <t>23명</t>
-  </si>
-  <si>
-    <t>548조 7800억 4695만</t>
+    <t>22명</t>
+  </si>
+  <si>
+    <t>545조 6025억 4496만</t>
   </si>
   <si>
     <t>Lv. 7 핑덤 길드입니다 주 1회 토벌전 참여 필수 사유없는 미접 제외 퇴출없는 편안하고 부담없는 가족같은 분위기 핑덤으로 다시 만들어가겠습니다! 길드 가입 문의는 -&amp;gt; 지환이당</t>
@@ -792,15 +792,6 @@
     <t>35조 1514억 967만</t>
   </si>
   <si>
-    <t>단풍카우</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
-  </si>
-  <si>
-    <t>34조 8856억 2109만</t>
-  </si>
-  <si>
     <t>아르미느</t>
   </si>
   <si>
@@ -945,7 +936,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EB%B2%A0%EB%A6%AC</t>
   </si>
   <si>
-    <t>159조 406억 3825만</t>
+    <t>159조 3907억 270만</t>
   </si>
   <si>
     <t>양시</t>
@@ -1833,7 +1824,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%91%EA%B5%AC</t>
   </si>
   <si>
-    <t>41조 7861억 8048만</t>
+    <t>42조 2513억 375만</t>
   </si>
   <si>
     <t>mumu5</t>
@@ -1872,15 +1863,6 @@
     <t>8조 6504억 7197만</t>
   </si>
   <si>
-    <t>확률단속</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%95%EB%A5%A0%EB%8B%A8%EC%86%8D</t>
-  </si>
-  <si>
-    <t>7조 7023억 931만</t>
-  </si>
-  <si>
     <t>꼼웅</t>
   </si>
   <si>
@@ -1914,7 +1896,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EB%8B%A8%EC%9E%A5</t>
   </si>
   <si>
-    <t>145조 1670억 1279만</t>
+    <t>149조 9766억 6007만</t>
   </si>
   <si>
     <t>순운</t>
@@ -1926,15 +1908,6 @@
     <t>36조 7129억 5745만</t>
   </si>
   <si>
-    <t>군고마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EA%B3%A0%EB%A7%88</t>
-  </si>
-  <si>
-    <t>8조 141억 1627만</t>
-  </si>
-  <si>
     <t>시온이아부지</t>
   </si>
   <si>
@@ -1950,7 +1923,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%8C%EB%A0%99%EC%BB%A4%ED%94%BC</t>
   </si>
   <si>
-    <t>5조 6547억 9625만</t>
+    <t>5조 6757억 6602만</t>
   </si>
   <si>
     <t>뙈지두루치기</t>
@@ -2073,7 +2046,7 @@
     <t>98</t>
   </si>
   <si>
-    <t>8984억 9431만</t>
+    <t>9230억 9529만</t>
   </si>
   <si>
     <t>짱죠a</t>
@@ -2091,7 +2064,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EC%9A%A9</t>
   </si>
   <si>
-    <t>4849억 5105만</t>
+    <t>4861억 7754만</t>
   </si>
   <si>
     <t>크림푸딩</t>
@@ -3812,7 +3785,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -4324,10 +4297,10 @@
         <v>86</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>149</v>
+        <v>98</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>109</v>
+        <v>155</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>255</v>
@@ -4356,7 +4329,7 @@
         <v>86</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>98</v>
+        <v>149</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>155</v>
@@ -4420,13 +4393,13 @@
         <v>86</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>149</v>
+        <v>264</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>155</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4440,22 +4413,22 @@
         <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>267</v>
+        <v>104</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>268</v>
@@ -4484,7 +4457,7 @@
         <v>86</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>150</v>
@@ -4516,10 +4489,10 @@
         <v>86</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>150</v>
+        <v>188</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>274</v>
@@ -4548,7 +4521,7 @@
         <v>86</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>188</v>
@@ -4580,10 +4553,10 @@
         <v>86</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>118</v>
+        <v>264</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>280</v>
@@ -4612,10 +4585,10 @@
         <v>86</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>267</v>
+        <v>233</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>283</v>
@@ -4644,10 +4617,10 @@
         <v>86</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>233</v>
+        <v>118</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>286</v>
@@ -4676,7 +4649,7 @@
         <v>86</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>150</v>
@@ -4708,10 +4681,10 @@
         <v>86</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>150</v>
+        <v>188</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>292</v>
@@ -4720,40 +4693,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J29"/>
+  <autoFilter ref="A1:J28"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -4782,7 +4723,6 @@
     <hyperlink ref="E26" r:id="rId25"/>
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4843,13 +4783,13 @@
         <v>83</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>86</v>
@@ -4858,10 +4798,10 @@
         <v>104</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>99</v>
+        <v>212</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4875,25 +4815,25 @@
         <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>99</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4907,13 +4847,13 @@
         <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>86</v>
@@ -4925,7 +4865,7 @@
         <v>212</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4939,13 +4879,13 @@
         <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>86</v>
@@ -4957,7 +4897,7 @@
         <v>212</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4971,13 +4911,13 @@
         <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>86</v>
@@ -4989,7 +4929,7 @@
         <v>99</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5003,13 +4943,13 @@
         <v>111</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>86</v>
@@ -5021,7 +4961,7 @@
         <v>109</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5041,7 +4981,7 @@
         <v>42</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>117</v>
@@ -5053,7 +4993,7 @@
         <v>99</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5067,13 +5007,13 @@
         <v>120</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>86</v>
@@ -5085,7 +5025,7 @@
         <v>99</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5099,13 +5039,13 @@
         <v>124</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>86</v>
@@ -5117,7 +5057,7 @@
         <v>99</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5131,13 +5071,13 @@
         <v>129</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>86</v>
@@ -5149,7 +5089,7 @@
         <v>99</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5163,13 +5103,13 @@
         <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>86</v>
@@ -5181,7 +5121,7 @@
         <v>99</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5195,13 +5135,13 @@
         <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>86</v>
@@ -5213,7 +5153,7 @@
         <v>99</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5227,13 +5167,13 @@
         <v>142</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>86</v>
@@ -5245,7 +5185,7 @@
         <v>99</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5259,13 +5199,13 @@
         <v>146</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>86</v>
@@ -5277,7 +5217,7 @@
         <v>109</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5291,13 +5231,13 @@
         <v>152</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>86</v>
@@ -5309,7 +5249,7 @@
         <v>140</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5323,13 +5263,13 @@
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>86</v>
@@ -5341,7 +5281,7 @@
         <v>109</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5355,13 +5295,13 @@
         <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>86</v>
@@ -5373,7 +5313,7 @@
         <v>109</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5387,25 +5327,25 @@
         <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>99</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5419,13 +5359,13 @@
         <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>86</v>
@@ -5437,7 +5377,7 @@
         <v>109</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5451,13 +5391,13 @@
         <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>86</v>
@@ -5469,7 +5409,7 @@
         <v>99</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5483,25 +5423,25 @@
         <v>177</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>140</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5515,13 +5455,13 @@
         <v>181</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>86</v>
@@ -5533,7 +5473,7 @@
         <v>140</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5547,13 +5487,13 @@
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>86</v>
@@ -5565,7 +5505,7 @@
         <v>109</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5579,13 +5519,13 @@
         <v>190</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>86</v>
@@ -5597,7 +5537,7 @@
         <v>140</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5611,13 +5551,13 @@
         <v>194</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>86</v>
@@ -5629,7 +5569,7 @@
         <v>140</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5643,13 +5583,13 @@
         <v>198</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>86</v>
@@ -5661,7 +5601,7 @@
         <v>140</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5675,13 +5615,13 @@
         <v>202</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>86</v>
@@ -5693,7 +5633,7 @@
         <v>140</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5707,13 +5647,13 @@
         <v>206</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>86</v>
@@ -5725,7 +5665,7 @@
         <v>150</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5736,16 +5676,16 @@
         <v>35</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>86</v>
@@ -5757,7 +5697,7 @@
         <v>155</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5768,16 +5708,16 @@
         <v>35</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>86</v>
@@ -5789,7 +5729,7 @@
         <v>155</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5888,13 +5828,13 @@
         <v>83</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>86</v>
@@ -5906,7 +5846,7 @@
         <v>93</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5920,13 +5860,13 @@
         <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>86</v>
@@ -5938,7 +5878,7 @@
         <v>88</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5952,13 +5892,13 @@
         <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>86</v>
@@ -5970,7 +5910,7 @@
         <v>109</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5984,13 +5924,13 @@
         <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>86</v>
@@ -6002,7 +5942,7 @@
         <v>99</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6016,13 +5956,13 @@
         <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>86</v>
@@ -6034,7 +5974,7 @@
         <v>109</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6048,13 +5988,13 @@
         <v>111</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>86</v>
@@ -6066,7 +6006,7 @@
         <v>140</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6080,13 +6020,13 @@
         <v>115</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>86</v>
@@ -6098,7 +6038,7 @@
         <v>140</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6112,13 +6052,13 @@
         <v>120</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>86</v>
@@ -6130,7 +6070,7 @@
         <v>155</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6144,13 +6084,13 @@
         <v>124</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>86</v>
@@ -6162,7 +6102,7 @@
         <v>140</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6176,13 +6116,13 @@
         <v>129</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>86</v>
@@ -6194,7 +6134,7 @@
         <v>155</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6208,25 +6148,25 @@
         <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>140</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6240,13 +6180,13 @@
         <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>86</v>
@@ -6258,7 +6198,7 @@
         <v>140</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6272,13 +6212,13 @@
         <v>142</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>86</v>
@@ -6290,7 +6230,7 @@
         <v>140</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6304,13 +6244,13 @@
         <v>146</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>86</v>
@@ -6322,7 +6262,7 @@
         <v>140</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6342,7 +6282,7 @@
         <v>50</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>117</v>
@@ -6354,7 +6294,7 @@
         <v>155</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6368,13 +6308,13 @@
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>86</v>
@@ -6386,7 +6326,7 @@
         <v>188</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6400,13 +6340,13 @@
         <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>86</v>
@@ -6418,7 +6358,7 @@
         <v>155</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6432,13 +6372,13 @@
         <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>86</v>
@@ -6450,7 +6390,7 @@
         <v>155</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6464,13 +6404,13 @@
         <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>86</v>
@@ -6482,7 +6422,7 @@
         <v>150</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6496,25 +6436,25 @@
         <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>155</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6528,25 +6468,25 @@
         <v>177</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>155</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6560,25 +6500,25 @@
         <v>181</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>155</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6592,13 +6532,13 @@
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>86</v>
@@ -6610,7 +6550,7 @@
         <v>155</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6624,13 +6564,13 @@
         <v>190</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>86</v>
@@ -6642,7 +6582,7 @@
         <v>150</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6656,13 +6596,13 @@
         <v>194</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>86</v>
@@ -6674,7 +6614,7 @@
         <v>150</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6688,13 +6628,13 @@
         <v>198</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>86</v>
@@ -6706,7 +6646,7 @@
         <v>188</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6720,13 +6660,13 @@
         <v>202</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>86</v>
@@ -6738,7 +6678,7 @@
         <v>150</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6752,13 +6692,13 @@
         <v>206</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>86</v>
@@ -6770,7 +6710,7 @@
         <v>150</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6781,16 +6721,16 @@
         <v>43</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>86</v>
@@ -6802,7 +6742,7 @@
         <v>188</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6813,16 +6753,16 @@
         <v>43</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>86</v>
@@ -6831,10 +6771,10 @@
         <v>233</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6939,7 +6879,7 @@
         <v>57</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>117</v>
@@ -6951,7 +6891,7 @@
         <v>212</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6965,13 +6905,13 @@
         <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>86</v>
@@ -6983,7 +6923,7 @@
         <v>99</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6997,13 +6937,13 @@
         <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>86</v>
@@ -7015,7 +6955,7 @@
         <v>140</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -7029,13 +6969,13 @@
         <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>86</v>
@@ -7047,7 +6987,7 @@
         <v>99</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -7061,13 +7001,13 @@
         <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>86</v>
@@ -7079,7 +7019,7 @@
         <v>99</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -7093,13 +7033,13 @@
         <v>111</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>86</v>
@@ -7111,7 +7051,7 @@
         <v>109</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -7125,13 +7065,13 @@
         <v>115</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>86</v>
@@ -7143,7 +7083,7 @@
         <v>99</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -7157,25 +7097,25 @@
         <v>120</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>109</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -7189,25 +7129,25 @@
         <v>124</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>109</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -7221,13 +7161,13 @@
         <v>129</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>86</v>
@@ -7239,7 +7179,7 @@
         <v>109</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -7253,13 +7193,13 @@
         <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>86</v>
@@ -7271,7 +7211,7 @@
         <v>109</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -7285,13 +7225,13 @@
         <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>86</v>
@@ -7303,7 +7243,7 @@
         <v>99</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -7317,13 +7257,13 @@
         <v>142</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>86</v>
@@ -7335,7 +7275,7 @@
         <v>109</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -7349,13 +7289,13 @@
         <v>146</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>86</v>
@@ -7367,7 +7307,7 @@
         <v>109</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -7381,13 +7321,13 @@
         <v>152</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>86</v>
@@ -7399,7 +7339,7 @@
         <v>140</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -7413,13 +7353,13 @@
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>86</v>
@@ -7431,7 +7371,7 @@
         <v>109</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7445,13 +7385,13 @@
         <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>86</v>
@@ -7463,7 +7403,7 @@
         <v>109</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7477,13 +7417,13 @@
         <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>86</v>
@@ -7495,7 +7435,7 @@
         <v>140</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7509,13 +7449,13 @@
         <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>86</v>
@@ -7527,7 +7467,7 @@
         <v>109</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7541,13 +7481,13 @@
         <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>86</v>
@@ -7559,7 +7499,7 @@
         <v>109</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7573,25 +7513,25 @@
         <v>177</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>155</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7605,13 +7545,13 @@
         <v>181</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>86</v>
@@ -7623,7 +7563,7 @@
         <v>155</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7637,25 +7577,25 @@
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>150</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7669,13 +7609,13 @@
         <v>190</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>86</v>
@@ -7687,7 +7627,7 @@
         <v>150</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7701,13 +7641,13 @@
         <v>194</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>86</v>
@@ -7719,7 +7659,7 @@
         <v>150</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7733,13 +7673,13 @@
         <v>198</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>86</v>
@@ -7751,7 +7691,7 @@
         <v>150</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -7765,13 +7705,13 @@
         <v>202</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>86</v>
@@ -7783,7 +7723,7 @@
         <v>155</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7797,13 +7737,13 @@
         <v>206</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>86</v>
@@ -7815,7 +7755,7 @@
         <v>150</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -7826,16 +7766,16 @@
         <v>51</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>86</v>
@@ -7847,7 +7787,7 @@
         <v>188</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -7858,16 +7798,16 @@
         <v>51</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>86</v>
@@ -7879,7 +7819,7 @@
         <v>150</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -7925,7 +7865,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -7978,13 +7918,13 @@
         <v>83</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>86</v>
@@ -7996,7 +7936,7 @@
         <v>88</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -8010,13 +7950,13 @@
         <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>86</v>
@@ -8028,7 +7968,7 @@
         <v>93</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -8042,13 +7982,13 @@
         <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>86</v>
@@ -8060,7 +8000,7 @@
         <v>212</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -8074,13 +8014,13 @@
         <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>86</v>
@@ -8092,7 +8032,7 @@
         <v>99</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -8106,13 +8046,13 @@
         <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>86</v>
@@ -8124,7 +8064,7 @@
         <v>212</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -8138,13 +8078,13 @@
         <v>111</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>86</v>
@@ -8156,7 +8096,7 @@
         <v>109</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -8170,13 +8110,13 @@
         <v>115</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>86</v>
@@ -8188,7 +8128,7 @@
         <v>99</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -8202,13 +8142,13 @@
         <v>120</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>86</v>
@@ -8220,7 +8160,7 @@
         <v>109</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -8234,13 +8174,13 @@
         <v>124</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>86</v>
@@ -8252,7 +8192,7 @@
         <v>109</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -8266,13 +8206,13 @@
         <v>129</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>86</v>
@@ -8284,7 +8224,7 @@
         <v>140</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -8298,13 +8238,13 @@
         <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>86</v>
@@ -8316,7 +8256,7 @@
         <v>109</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -8330,13 +8270,13 @@
         <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>86</v>
@@ -8348,7 +8288,7 @@
         <v>140</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -8362,13 +8302,13 @@
         <v>142</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>86</v>
@@ -8380,7 +8320,7 @@
         <v>150</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -8394,13 +8334,13 @@
         <v>146</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>86</v>
@@ -8412,7 +8352,7 @@
         <v>150</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -8426,13 +8366,13 @@
         <v>152</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>86</v>
@@ -8444,7 +8384,7 @@
         <v>188</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -8458,25 +8398,25 @@
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>87</v>
+        <v>264</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>188</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -8490,64 +8430,32 @@
         <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>188</v>
+        <v>474</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J19"/>
+  <autoFilter ref="A1:J18"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -8566,7 +8474,6 @@
     <hyperlink ref="E16" r:id="rId15"/>
     <hyperlink ref="E17" r:id="rId16"/>
     <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8574,7 +8481,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -8627,13 +8534,13 @@
         <v>83</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>86</v>
@@ -8645,7 +8552,7 @@
         <v>99</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -8659,13 +8566,13 @@
         <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>86</v>
@@ -8677,7 +8584,7 @@
         <v>109</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -8691,13 +8598,13 @@
         <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>86</v>
@@ -8709,7 +8616,7 @@
         <v>155</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -8723,25 +8630,25 @@
         <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>188</v>
+        <v>474</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -8755,25 +8662,25 @@
         <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -8787,13 +8694,13 @@
         <v>111</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>86</v>
@@ -8802,10 +8709,10 @@
         <v>104</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -8819,25 +8726,25 @@
         <v>115</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>104</v>
+        <v>345</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -8851,25 +8758,25 @@
         <v>120</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>348</v>
+        <v>104</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>477</v>
+        <v>639</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -8883,25 +8790,25 @@
         <v>124</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>648</v>
+        <v>188</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -8915,25 +8822,25 @@
         <v>129</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>650</v>
+        <v>74</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>650</v>
+        <v>74</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>87</v>
+        <v>345</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>188</v>
+        <v>474</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -8947,25 +8854,25 @@
         <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>74</v>
+        <v>646</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>74</v>
+        <v>646</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>348</v>
+        <v>118</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -8979,25 +8886,25 @@
         <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>477</v>
+        <v>639</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -9011,25 +8918,25 @@
         <v>142</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>648</v>
+        <v>474</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -9043,25 +8950,25 @@
         <v>146</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>477</v>
+        <v>639</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -9075,25 +8982,25 @@
         <v>152</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>648</v>
+        <v>639</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -9107,25 +9014,25 @@
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>149</v>
+        <v>264</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>648</v>
+        <v>663</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -9139,25 +9046,25 @@
         <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>267</v>
+        <v>98</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>672</v>
+        <v>639</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -9171,25 +9078,25 @@
         <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>98</v>
+        <v>264</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>648</v>
+        <v>670</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -9203,25 +9110,25 @@
         <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>267</v>
+        <v>149</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>679</v>
+        <v>670</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -9235,25 +9142,25 @@
         <v>173</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>149</v>
+        <v>233</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>679</v>
+        <v>670</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -9267,13 +9174,13 @@
         <v>177</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>86</v>
@@ -9282,10 +9189,10 @@
         <v>233</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>679</v>
+        <v>670</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -9299,13 +9206,13 @@
         <v>181</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>86</v>
@@ -9314,49 +9221,17 @@
         <v>233</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>679</v>
+        <v>663</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J24"/>
+  <autoFilter ref="A1:J23"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -9380,7 +9255,6 @@
     <hyperlink ref="E21" r:id="rId20"/>
     <hyperlink ref="E22" r:id="rId21"/>
     <hyperlink ref="E23" r:id="rId22"/>
-    <hyperlink ref="E24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
